--- a/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.265449656101135</v>
+        <v>1.300743486068808</v>
       </c>
       <c r="C3" t="n">
-        <v>4.607211294645778</v>
+        <v>4.624696221258414</v>
       </c>
       <c r="D3" t="n">
-        <v>6.045244118774448</v>
+        <v>6.069139857895816</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91790506952136</v>
+        <v>11.99457956522304</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.413924828551296</v>
+        <v>1.49882301156008</v>
       </c>
       <c r="C4" t="n">
-        <v>5.09333991209165</v>
+        <v>5.150928974885273</v>
       </c>
       <c r="D4" t="n">
-        <v>6.28405582910541</v>
+        <v>6.282944904090019</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79132056974835</v>
+        <v>12.93269689053537</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.614667835916179</v>
+        <v>1.754662318520807</v>
       </c>
       <c r="C5" t="n">
-        <v>5.717323919039514</v>
+        <v>5.880609445475255</v>
       </c>
       <c r="D5" t="n">
-        <v>6.564522091362742</v>
+        <v>6.540421158504918</v>
       </c>
       <c r="E5" t="n">
-        <v>13.89651384631843</v>
+        <v>14.17569292250098</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.839622485231676</v>
+        <v>2.033692364000924</v>
       </c>
       <c r="C6" t="n">
-        <v>6.499636001146297</v>
+        <v>6.814568419490476</v>
       </c>
       <c r="D6" t="n">
-        <v>6.928135844625461</v>
+        <v>6.806427879775423</v>
       </c>
       <c r="E6" t="n">
-        <v>15.26739433100343</v>
+        <v>15.65468866326682</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.091409000567204</v>
+        <v>2.339370086254357</v>
       </c>
       <c r="C7" t="n">
-        <v>7.476639655444878</v>
+        <v>7.911865665308606</v>
       </c>
       <c r="D7" t="n">
-        <v>7.266762508554409</v>
+        <v>7.148838990144465</v>
       </c>
       <c r="E7" t="n">
-        <v>16.83481116456649</v>
+        <v>17.40007474170743</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.298618848257876</v>
+        <v>1.495315681116096</v>
       </c>
       <c r="C8" t="n">
-        <v>5.255787840247132</v>
+        <v>5.619407696704907</v>
       </c>
       <c r="D8" t="n">
-        <v>5.537490712183153</v>
+        <v>5.349247516954035</v>
       </c>
       <c r="E8" t="n">
-        <v>12.09189740068816</v>
+        <v>12.46397089477504</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.628197401235256</v>
+        <v>1.884047576168894</v>
       </c>
       <c r="C9" t="n">
-        <v>6.566016402926255</v>
+        <v>7.028970381273364</v>
       </c>
       <c r="D9" t="n">
-        <v>6.035319510320551</v>
+        <v>5.821320948013128</v>
       </c>
       <c r="E9" t="n">
-        <v>14.22953331448206</v>
+        <v>14.73433890545539</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.989355866786711</v>
+        <v>2.277999535518192</v>
       </c>
       <c r="C10" t="n">
-        <v>8.033173100598665</v>
+        <v>8.592174249319363</v>
       </c>
       <c r="D10" t="n">
-        <v>6.51061820410863</v>
+        <v>6.275066120203802</v>
       </c>
       <c r="E10" t="n">
-        <v>16.53314717149401</v>
+        <v>17.14523990504136</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.343430681332825</v>
+        <v>2.67268564117013</v>
       </c>
       <c r="C11" t="n">
-        <v>9.584575969808116</v>
+        <v>10.24539364793314</v>
       </c>
       <c r="D11" t="n">
-        <v>6.979057899819047</v>
+        <v>6.730189997959943</v>
       </c>
       <c r="E11" t="n">
-        <v>18.90706455095999</v>
+        <v>19.64826928706321</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.692450493268785</v>
+        <v>3.051922043002875</v>
       </c>
       <c r="C12" t="n">
-        <v>11.20477311792661</v>
+        <v>12.02536177935958</v>
       </c>
       <c r="D12" t="n">
-        <v>7.429846441273618</v>
+        <v>7.140377501443571</v>
       </c>
       <c r="E12" t="n">
-        <v>21.32707005246901</v>
+        <v>22.21766132380602</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.032427898208516</v>
+        <v>3.40402359484937</v>
       </c>
       <c r="C13" t="n">
-        <v>12.87226187753286</v>
+        <v>13.83029173666498</v>
       </c>
       <c r="D13" t="n">
-        <v>7.865760474278482</v>
+        <v>7.492791697890262</v>
       </c>
       <c r="E13" t="n">
-        <v>23.77045025001986</v>
+        <v>24.72710702940461</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.747775985439469</v>
+        <v>1.962366398633737</v>
       </c>
       <c r="C14" t="n">
-        <v>8.943348521560829</v>
+        <v>9.646800204084796</v>
       </c>
       <c r="D14" t="n">
-        <v>5.979422750008581</v>
+        <v>5.724708308141746</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67054725700888</v>
+        <v>17.33387491086028</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.79224915644185</v>
+        <v>1.990130223709837</v>
       </c>
       <c r="C15" t="n">
-        <v>9.692539829625655</v>
+        <v>10.53638143385692</v>
       </c>
       <c r="D15" t="n">
-        <v>5.962055633120455</v>
+        <v>5.674334833436842</v>
       </c>
       <c r="E15" t="n">
-        <v>17.44684461918796</v>
+        <v>18.2008464910036</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.072223966738955</v>
+        <v>2.281522759807332</v>
       </c>
       <c r="C16" t="n">
-        <v>11.46412319689311</v>
+        <v>12.49896381698559</v>
       </c>
       <c r="D16" t="n">
-        <v>6.446548125166256</v>
+        <v>6.02361121417673</v>
       </c>
       <c r="E16" t="n">
-        <v>19.98289528879832</v>
+        <v>20.80409779096965</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.656944687842554</v>
+        <v>1.806621942832023</v>
       </c>
       <c r="C17" t="n">
-        <v>10.56656035828546</v>
+        <v>11.54953524716258</v>
       </c>
       <c r="D17" t="n">
-        <v>5.969094764159904</v>
+        <v>5.532109043522606</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19259981028792</v>
+        <v>18.88826623351721</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.883826582293992</v>
+        <v>2.042427923915064</v>
       </c>
       <c r="C18" t="n">
-        <v>12.32400655861176</v>
+        <v>13.46417888989288</v>
       </c>
       <c r="D18" t="n">
-        <v>6.39529107752753</v>
+        <v>5.91000336984129</v>
       </c>
       <c r="E18" t="n">
-        <v>20.60312421843329</v>
+        <v>21.41661018364923</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.884680702796687</v>
+        <v>2.027034119912475</v>
       </c>
       <c r="C19" t="n">
-        <v>13.15508544268781</v>
+        <v>14.38030657758783</v>
       </c>
       <c r="D19" t="n">
-        <v>6.488242950165618</v>
+        <v>5.94294100531877</v>
       </c>
       <c r="E19" t="n">
-        <v>21.52800909565012</v>
+        <v>22.35028170281908</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.095167410587203</v>
+        <v>2.245630063740069</v>
       </c>
       <c r="C20" t="n">
-        <v>15.1306858003748</v>
+        <v>16.37735812261261</v>
       </c>
       <c r="D20" t="n">
-        <v>6.916864180362732</v>
+        <v>6.23451025600303</v>
       </c>
       <c r="E20" t="n">
-        <v>24.14271739132473</v>
+        <v>24.85749844235571</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.242961315915759</v>
+        <v>1.332369079341516</v>
       </c>
       <c r="C21" t="n">
-        <v>11.10032676760741</v>
+        <v>11.88500825518076</v>
       </c>
       <c r="D21" t="n">
-        <v>5.778243010454324</v>
+        <v>5.162265048378748</v>
       </c>
       <c r="E21" t="n">
-        <v>18.1215310939775</v>
+        <v>18.37964238290103</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.300743486068808</v>
+        <v>1.246786632243403</v>
       </c>
       <c r="C3" t="n">
-        <v>4.624696221258414</v>
+        <v>4.612434192432371</v>
       </c>
       <c r="D3" t="n">
-        <v>6.069139857895816</v>
+        <v>6.041356397865631</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99457956522304</v>
+        <v>11.9005772225414</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.49882301156008</v>
+        <v>1.36331871808655</v>
       </c>
       <c r="C4" t="n">
-        <v>5.150928974885273</v>
+        <v>5.077146877984938</v>
       </c>
       <c r="D4" t="n">
-        <v>6.282944904090019</v>
+        <v>6.355723762537683</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93269689053537</v>
+        <v>12.79618935860917</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.754662318520807</v>
+        <v>1.532448955893886</v>
       </c>
       <c r="C5" t="n">
-        <v>5.880609445475255</v>
+        <v>5.651433088394897</v>
       </c>
       <c r="D5" t="n">
-        <v>6.540421158504918</v>
+        <v>6.631497444000855</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17569292250098</v>
+        <v>13.81537948828964</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.033692364000924</v>
+        <v>1.739728776414303</v>
       </c>
       <c r="C6" t="n">
-        <v>6.814568419490476</v>
+        <v>6.346853019454231</v>
       </c>
       <c r="D6" t="n">
-        <v>6.806427879775423</v>
+        <v>6.943839616929516</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65468866326682</v>
+        <v>15.03042141279805</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.339370086254357</v>
+        <v>1.976141667639573</v>
       </c>
       <c r="C7" t="n">
-        <v>7.911865665308606</v>
+        <v>7.173254522092575</v>
       </c>
       <c r="D7" t="n">
-        <v>7.148838990144465</v>
+        <v>7.256166050724852</v>
       </c>
       <c r="E7" t="n">
-        <v>17.40007474170743</v>
+        <v>16.405562240457</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.495315681116096</v>
+        <v>1.236170033480024</v>
       </c>
       <c r="C8" t="n">
-        <v>5.619407696704907</v>
+        <v>4.783726044558878</v>
       </c>
       <c r="D8" t="n">
-        <v>5.349247516954035</v>
+        <v>5.397331618703324</v>
       </c>
       <c r="E8" t="n">
-        <v>12.46397089477504</v>
+        <v>11.41722769674223</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.884047576168894</v>
+        <v>1.584102286209031</v>
       </c>
       <c r="C9" t="n">
-        <v>7.028970381273364</v>
+        <v>5.776753676122873</v>
       </c>
       <c r="D9" t="n">
-        <v>5.821320948013128</v>
+        <v>5.803469431614576</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73433890545539</v>
+        <v>13.16432539394648</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.277999535518192</v>
+        <v>1.953603350804062</v>
       </c>
       <c r="C10" t="n">
-        <v>8.592174249319363</v>
+        <v>6.928503418907772</v>
       </c>
       <c r="D10" t="n">
-        <v>6.275066120203802</v>
+        <v>6.267422398218631</v>
       </c>
       <c r="E10" t="n">
-        <v>17.14523990504136</v>
+        <v>15.14952916793046</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.67268564117013</v>
+        <v>2.3503069909367</v>
       </c>
       <c r="C11" t="n">
-        <v>10.24539364793314</v>
+        <v>8.177342851275551</v>
       </c>
       <c r="D11" t="n">
-        <v>6.730189997959943</v>
+        <v>6.685738360246861</v>
       </c>
       <c r="E11" t="n">
-        <v>19.64826928706321</v>
+        <v>17.21338820245911</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.051922043002875</v>
+        <v>2.75549504165676</v>
       </c>
       <c r="C12" t="n">
-        <v>12.02536177935958</v>
+        <v>9.508859694049642</v>
       </c>
       <c r="D12" t="n">
-        <v>7.140377501443571</v>
+        <v>7.110354628776395</v>
       </c>
       <c r="E12" t="n">
-        <v>22.21766132380602</v>
+        <v>19.3747093644828</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.40402359484937</v>
+        <v>3.165910875630719</v>
       </c>
       <c r="C13" t="n">
-        <v>13.83029173666498</v>
+        <v>10.90781195110933</v>
       </c>
       <c r="D13" t="n">
-        <v>7.492791697890262</v>
+        <v>7.552824845457879</v>
       </c>
       <c r="E13" t="n">
-        <v>24.72710702940461</v>
+        <v>21.62654767219792</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.962366398633737</v>
+        <v>1.822928772199562</v>
       </c>
       <c r="C14" t="n">
-        <v>9.646800204084796</v>
+        <v>7.731950394336605</v>
       </c>
       <c r="D14" t="n">
-        <v>5.724708308141746</v>
+        <v>5.742487759065655</v>
       </c>
       <c r="E14" t="n">
-        <v>17.33387491086028</v>
+        <v>15.29736692560182</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.990130223709837</v>
+        <v>1.909450197374834</v>
       </c>
       <c r="C15" t="n">
-        <v>10.53638143385692</v>
+        <v>8.263782760681186</v>
       </c>
       <c r="D15" t="n">
-        <v>5.674334833436842</v>
+        <v>5.716432174994946</v>
       </c>
       <c r="E15" t="n">
-        <v>18.2008464910036</v>
+        <v>15.88966513305097</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.281522759807332</v>
+        <v>2.272736117854324</v>
       </c>
       <c r="C16" t="n">
-        <v>12.49896381698559</v>
+        <v>9.742461700386604</v>
       </c>
       <c r="D16" t="n">
-        <v>6.02361121417673</v>
+        <v>6.145004317806849</v>
       </c>
       <c r="E16" t="n">
-        <v>20.80409779096965</v>
+        <v>18.16020213604778</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.806621942832023</v>
+        <v>1.861000948170254</v>
       </c>
       <c r="C17" t="n">
-        <v>11.54953524716258</v>
+        <v>8.972899127458659</v>
       </c>
       <c r="D17" t="n">
-        <v>5.532109043522606</v>
+        <v>5.677898577603258</v>
       </c>
       <c r="E17" t="n">
-        <v>18.88826623351721</v>
+        <v>16.51179865323217</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.042427923915064</v>
+        <v>2.172872741378339</v>
       </c>
       <c r="C18" t="n">
-        <v>13.46417888989288</v>
+        <v>10.46698168864371</v>
       </c>
       <c r="D18" t="n">
-        <v>5.91000336984129</v>
+        <v>6.109445415959028</v>
       </c>
       <c r="E18" t="n">
-        <v>21.41661018364923</v>
+        <v>18.74929984598108</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.027034119912475</v>
+        <v>2.224659932777358</v>
       </c>
       <c r="C19" t="n">
-        <v>14.38030657758783</v>
+        <v>11.21109736107758</v>
       </c>
       <c r="D19" t="n">
-        <v>5.94294100531877</v>
+        <v>6.209357879820226</v>
       </c>
       <c r="E19" t="n">
-        <v>22.35028170281908</v>
+        <v>19.64511517367516</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.245630063740069</v>
+        <v>2.530022738706285</v>
       </c>
       <c r="C20" t="n">
-        <v>16.37735812261261</v>
+        <v>12.94147677719779</v>
       </c>
       <c r="D20" t="n">
-        <v>6.23451025600303</v>
+        <v>6.713406786134624</v>
       </c>
       <c r="E20" t="n">
-        <v>24.85749844235571</v>
+        <v>22.1849063020387</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.332369079341516</v>
+        <v>1.532262729403209</v>
       </c>
       <c r="C21" t="n">
-        <v>11.88500825518076</v>
+        <v>9.571902671727807</v>
       </c>
       <c r="D21" t="n">
-        <v>5.162265048378748</v>
+        <v>5.610315065642908</v>
       </c>
       <c r="E21" t="n">
-        <v>18.37964238290103</v>
+        <v>16.71448046677392</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_48_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.246786632243403</v>
+        <v>2.623435554648898</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612434192432371</v>
+        <v>7.652190380200101</v>
       </c>
       <c r="D3" t="n">
-        <v>6.041356397865631</v>
+        <v>8.184740058069698</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9005772225414</v>
+        <v>18.4603659929187</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.36331871808655</v>
+        <v>1.159782065820071</v>
       </c>
       <c r="C4" t="n">
-        <v>5.077146877984938</v>
+        <v>4.388257252206885</v>
       </c>
       <c r="D4" t="n">
-        <v>6.355723762537683</v>
+        <v>5.792527721743459</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79618935860917</v>
+        <v>11.34056703977041</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.532448955893886</v>
+        <v>1.340567079640498</v>
       </c>
       <c r="C5" t="n">
-        <v>5.651433088394897</v>
+        <v>4.911200290400393</v>
       </c>
       <c r="D5" t="n">
-        <v>6.631497444000855</v>
+        <v>6.055462045074394</v>
       </c>
       <c r="E5" t="n">
-        <v>13.81537948828964</v>
+        <v>12.30722941511528</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739728776414303</v>
+        <v>1.535375695093987</v>
       </c>
       <c r="C6" t="n">
-        <v>6.346853019454231</v>
+        <v>5.568519291148833</v>
       </c>
       <c r="D6" t="n">
-        <v>6.943839616929516</v>
+        <v>6.343392758966749</v>
       </c>
       <c r="E6" t="n">
-        <v>15.03042141279805</v>
+        <v>13.44728774520957</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.976141667639573</v>
+        <v>1.733832332630541</v>
       </c>
       <c r="C7" t="n">
-        <v>7.173254522092575</v>
+        <v>6.356322071162942</v>
       </c>
       <c r="D7" t="n">
-        <v>7.256166050724852</v>
+        <v>6.750224828371656</v>
       </c>
       <c r="E7" t="n">
-        <v>16.405562240457</v>
+        <v>14.84037923216514</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.236170033480024</v>
+        <v>1.94555866722554</v>
       </c>
       <c r="C8" t="n">
-        <v>4.783726044558878</v>
+        <v>7.241263636540996</v>
       </c>
       <c r="D8" t="n">
-        <v>5.397331618703324</v>
+        <v>7.15926745334044</v>
       </c>
       <c r="E8" t="n">
-        <v>11.41722769674223</v>
+        <v>16.34608975710697</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.584102286209031</v>
+        <v>2.168423775001959</v>
       </c>
       <c r="C9" t="n">
-        <v>5.776753676122873</v>
+        <v>8.258464325232302</v>
       </c>
       <c r="D9" t="n">
-        <v>5.803469431614576</v>
+        <v>7.534016963468209</v>
       </c>
       <c r="E9" t="n">
-        <v>13.16432539394648</v>
+        <v>17.96090506370247</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.953603350804062</v>
+        <v>1.31416747690478</v>
       </c>
       <c r="C10" t="n">
-        <v>6.928503418907772</v>
+        <v>6.205666508452258</v>
       </c>
       <c r="D10" t="n">
-        <v>6.267422398218631</v>
+        <v>5.937983179412323</v>
       </c>
       <c r="E10" t="n">
-        <v>15.14952916793046</v>
+        <v>13.45781716476936</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.3503069909367</v>
+        <v>1.289564879436355</v>
       </c>
       <c r="C11" t="n">
-        <v>8.177342851275551</v>
+        <v>6.465731475307239</v>
       </c>
       <c r="D11" t="n">
-        <v>6.685738360246861</v>
+        <v>5.799537118159438</v>
       </c>
       <c r="E11" t="n">
-        <v>17.21338820245911</v>
+        <v>13.55483347290303</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.75549504165676</v>
+        <v>1.446281265465274</v>
       </c>
       <c r="C12" t="n">
-        <v>9.508859694049642</v>
+        <v>7.566143024566361</v>
       </c>
       <c r="D12" t="n">
-        <v>7.110354628776395</v>
+        <v>6.209082990463036</v>
       </c>
       <c r="E12" t="n">
-        <v>19.3747093644828</v>
+        <v>15.22150728049467</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.165910875630719</v>
+        <v>1.164195697604038</v>
       </c>
       <c r="C13" t="n">
-        <v>10.90781195110933</v>
+        <v>7.174857659561751</v>
       </c>
       <c r="D13" t="n">
-        <v>7.552824845457879</v>
+        <v>5.669239562851801</v>
       </c>
       <c r="E13" t="n">
-        <v>21.62654767219792</v>
+        <v>14.00829292001759</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.822928772199562</v>
+        <v>1.303005005507494</v>
       </c>
       <c r="C14" t="n">
-        <v>7.731950394336605</v>
+        <v>8.369340273841804</v>
       </c>
       <c r="D14" t="n">
-        <v>5.742487759065655</v>
+        <v>6.02023400207412</v>
       </c>
       <c r="E14" t="n">
-        <v>15.29736692560182</v>
+        <v>15.69257928142342</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.909450197374834</v>
+        <v>1.293570410069683</v>
       </c>
       <c r="C15" t="n">
-        <v>8.263782760681186</v>
+        <v>9.019964112400249</v>
       </c>
       <c r="D15" t="n">
-        <v>5.716432174994946</v>
+        <v>6.080699843178682</v>
       </c>
       <c r="E15" t="n">
-        <v>15.88966513305097</v>
+        <v>16.39423436564861</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.272736117854324</v>
+        <v>1.439634833507523</v>
       </c>
       <c r="C16" t="n">
-        <v>9.742461700386604</v>
+        <v>10.60949218539218</v>
       </c>
       <c r="D16" t="n">
-        <v>6.145004317806849</v>
+        <v>6.463826884761</v>
       </c>
       <c r="E16" t="n">
-        <v>18.16020213604778</v>
+        <v>18.5129539036607</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.861000948170254</v>
+        <v>0.864792100239888</v>
       </c>
       <c r="C17" t="n">
-        <v>8.972899127458659</v>
+        <v>8.085693727130817</v>
       </c>
       <c r="D17" t="n">
-        <v>5.677898577603258</v>
+        <v>5.365270838662903</v>
       </c>
       <c r="E17" t="n">
-        <v>16.51179865323217</v>
+        <v>14.31575666603361</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.172872741378339</v>
+        <v>0.6940858094254526</v>
       </c>
       <c r="C18" t="n">
-        <v>10.46698168864371</v>
+        <v>7.226487771328092</v>
       </c>
       <c r="D18" t="n">
-        <v>6.109445415959028</v>
+        <v>4.873307246587784</v>
       </c>
       <c r="E18" t="n">
-        <v>18.74929984598108</v>
+        <v>12.79388082734133</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.224659932777358</v>
+        <v>0.8226849412047422</v>
       </c>
       <c r="C19" t="n">
-        <v>11.21109736107758</v>
+        <v>9.05245996141082</v>
       </c>
       <c r="D19" t="n">
-        <v>6.209357879820226</v>
+        <v>5.343191332794393</v>
       </c>
       <c r="E19" t="n">
-        <v>19.64511517367516</v>
+        <v>15.21833623540996</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.530022738706285</v>
+        <v>0.9542882209590272</v>
       </c>
       <c r="C20" t="n">
-        <v>12.94147677719779</v>
+        <v>10.97762793953064</v>
       </c>
       <c r="D20" t="n">
-        <v>6.713406786134624</v>
+        <v>5.83737367468111</v>
       </c>
       <c r="E20" t="n">
-        <v>22.1849063020387</v>
+        <v>17.76928983517078</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.532262729403209</v>
+        <v>1.072745898953447</v>
       </c>
       <c r="C21" t="n">
-        <v>9.571902671727807</v>
+        <v>12.92473797884039</v>
       </c>
       <c r="D21" t="n">
-        <v>5.610315065642908</v>
+        <v>6.260202593423169</v>
       </c>
       <c r="E21" t="n">
-        <v>16.71448046677392</v>
+        <v>20.257686471217</v>
       </c>
     </row>
   </sheetData>
